--- a/data/trans_camb/P1412-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1412-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,69</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,57</t>
+          <t>-2,28; 0,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,65</t>
+          <t>-2,4; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,36</t>
+          <t>-1,86; 0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,14</t>
+          <t>-2,22; 0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,44</t>
+          <t>-1,66; 0,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,08</t>
+          <t>-1,76; 0,02</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-56,45%</t>
+          <t>-61,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-80,97%</t>
+          <t>-80,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-64,89%</t>
+          <t>-68,15%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 289,4</t>
+          <t>-100,0; 125,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,67</t>
+          <t>-100,0; 129,34</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,82</t>
+          <t>-0,34; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,16</t>
+          <t>-0,6; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,87</t>
+          <t>-1,03; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,55</t>
+          <t>-1,21; 0,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,06</t>
+          <t>-0,39; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,61</t>
+          <t>-0,66; 0,63</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,89%</t>
+          <t>-26,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 499,57</t>
+          <t>-58,81; 500,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,98; 321,9</t>
+          <t>-73,23; 343,71</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,98</t>
+          <t>0,63; 2,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,83</t>
+          <t>-0,23; 1,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,46</t>
+          <t>-0,49; 0,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,89</t>
+          <t>0,42; 1,92</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229,85%</t>
+          <t>224,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>664,05%</t>
+          <t>649,9%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,24</t>
+          <t>-0,55; 2,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,12</t>
+          <t>-0,04; 3,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,13</t>
+          <t>-2,14; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; -0,28</t>
+          <t>-2,73; -0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,06</t>
+          <t>-0,97; 1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,73</t>
+          <t>-1,07; 0,92</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>220,9%</t>
+          <t>207,81%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-93,59%</t>
+          <t>-92,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,58%</t>
+          <t>-6,97%</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,11; —</t>
+          <t>-46,94; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 295,97</t>
+          <t>-100,0; 307,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,02</t>
+          <t>-100,0; 56,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 233,52</t>
+          <t>-65,26; 251,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,61; 146,34</t>
+          <t>-70,8; 211,62</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,35</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,26</t>
+          <t>-6,01; -0,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,97</t>
+          <t>-6,94; -0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,0</t>
+          <t>-2,44; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,64</t>
+          <t>-1,75; 0,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,33</t>
+          <t>-3,56; -0,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,31</t>
+          <t>-3,45; -0,35</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-23,64%</t>
+          <t>-28,56%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-87,78%</t>
+          <t>-88,85%</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -35,61</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,26</t>
+          <t>0,8; 3,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,35</t>
+          <t>-3,32; -0,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,74</t>
+          <t>-2,46; 0,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,43</t>
+          <t>-1,17; 0,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,56</t>
+          <t>-0,43; 1,43</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-35,02%</t>
+          <t>-39,1%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>117,43%</t>
+          <t>111,2%</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 662,65</t>
+          <t>-56,48; 781,32</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,15</t>
+          <t>-0,9; 1,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,47</t>
+          <t>-0,65; 1,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,73</t>
+          <t>-0,48; 1,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,47</t>
+          <t>-0,68; 1,03</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,16</t>
+          <t>-0,44; 1,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,67</t>
+          <t>-0,43; 0,9</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-20,22%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-85,22; 427,2</t>
+          <t>-80,46; 601,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 560,96</t>
+          <t>-59,97; 494,51</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 690,32</t>
+          <t>-58,13; 696,08</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-85,5; 176,29</t>
+          <t>-65,63; 408,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 297,45</t>
+          <t>-46,89; 267,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 176,59</t>
+          <t>-42,9; 241,33</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,17 +1700,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,98</t>
+          <t>-0,5; 1,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,36</t>
+          <t>-0,97; 0,48</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,42</t>
+          <t>-0,82; 0,55</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,64</t>
+          <t>-0,69; 0,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,54</t>
+          <t>-0,51; 0,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,33</t>
+          <t>-0,57; 0,4</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-43,3%</t>
+          <t>-26,17%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-22,68%</t>
+          <t>-11,98%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-73,21; 491,19</t>
+          <t>-69,05; 833,41</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-94,98; 298,1</t>
+          <t>-100,0; 367,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,62</t>
+          <t>-100,0; 339,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 370,7</t>
+          <t>-75,88; 325,63</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 203,85</t>
+          <t>-65,03; 180,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-74,29; 113,65</t>
+          <t>-68,26; 159,63</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,5</t>
+          <t>-0,32; 0,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,61</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,23</t>
+          <t>-0,54; 0,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,13</t>
+          <t>-0,51; 0,19</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,24</t>
+          <t>-0,32; 0,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,26</t>
+          <t>-0,2; 0,33</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-19,37%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-1,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 116,14</t>
+          <t>-37,33; 130,17</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 136,02</t>
+          <t>-19,31; 157,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 51,07</t>
+          <t>-60,97; 45,79</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 27,17</t>
+          <t>-53,77; 45,03</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 46,1</t>
+          <t>-39,97; 42,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 51,74</t>
+          <t>-23,51; 67,19</t>
         </is>
       </c>
     </row>
